--- a/templates/异常表模板.xlsx
+++ b/templates/异常表模板.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="异常记录" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="异常记录" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,24 +440,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="17.6" customWidth="1" min="5" max="5"/>
+    <col width="19.8" customWidth="1" min="5" max="5"/>
     <col width="17.6" customWidth="1" min="6" max="6"/>
-    <col width="17.6" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="19.8" customWidth="1" min="7" max="7"/>
+    <col width="17.6" customWidth="1" min="8" max="8"/>
+    <col width="17.6" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="13.2" customWidth="1" min="12" max="12"/>
-    <col width="30.8" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="13.2" customWidth="1" min="14" max="14"/>
+    <col width="13.2" customWidth="1" min="15" max="15"/>
+    <col width="30.8" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -483,57 +487,77 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>T-1日*系统排班</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>T0日*系统排班</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>T+1日*系统排班</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>开始加班打卡时间</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>结束加班打卡时间</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>开始日期</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>结束日期</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>开始时间</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>结束时间</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>转换加班区间</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>上报加班时数</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>实际加班时数(未减吃饭时间)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>差异</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>提醒信息</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>就餐信息</t>
         </is>
       </c>
     </row>
@@ -558,47 +582,67 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>双班中班 2026-07-31 15:45:00~2026-08-01 00:20:00</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>双班早班 2026-08-01 07:00:00~2026-08-01 15:45:00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
+          <t>固定班 2026-08-02 08:45:00~2026-08-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>2026-08-01 16:56:29</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>20260801</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>20260801</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>15:45</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>18:45</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>15:45-18:45</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>3</v>
       </c>
-      <c r="M2" t="n">
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="N2" t="n">
+      <c r="Q2" t="n">
         <v>2</v>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>【加班结束卡】请确认加班结束时间</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
